--- a/Forkin-finding-2014-llama3.2.xlsx
+++ b/Forkin-finding-2014-llama3.2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>DOCUMENT</t>
   </si>
@@ -64,6 +64,18 @@
     <t>Summarize the coroner’s findings in 2-3 sentences</t>
   </si>
   <si>
+    <t>Did the coroner make recommendations for future prevention? If yes, what were they?</t>
+  </si>
+  <si>
+    <t>Differentiate between the immediate cause of death and contributing factors.</t>
+  </si>
+  <si>
+    <t>Did the coroner evaluate the adequacy of supervision, treatment, or care provided? Explain the conclusion.</t>
+  </si>
+  <si>
+    <t>Does this case highlight any broader patterns or lessons relevant to public safety or institutional care?</t>
+  </si>
+  <si>
     <t>The deceased was Luke Isaac Forkin, born in Western Australia on 23 October 1982 (page 4)</t>
   </si>
   <si>
@@ -97,17 +109,24 @@
     <t>The coroner found that Luke Forkin committed suicide by hanging while absent without leave from Graylands Hospital. The care, treatment, and supervision were reasonable and appropriate, and the decision to grant unescorted ground access was justified by his apparent stability (pages 20–21).</t>
   </si>
   <si>
-    <t>Based on the provided context information, the deceased was a person who:
-* Was born in Western Australia in 1982
-* Had a blended family background with three different relationships
-* Experienced a tumultuous childhood, including difficulties fitting in at school and truancy
-* Developed a history of drug abuse, including amphetamines, cannabis, heroin, LSD, ecstasy, and possibly alcohol
-* Suffered a serious accident involving a gunshot wound to the abdomen in 2002, which resulted in significant injuries and disability
-* Had a growing criminal record but had not yet been sentenced to detention or imprisonment
-Unfortunately, the context information does not provide a clear answer to who the deceased was beyond these details.</t>
-  </si>
-  <si>
-    <t>Based on the provided context information, it is stated that Mr Ward entered the house at about 4:00pm and found the deceased hanging by his neck with an electrical cord tied to a rafter through an open manhole in the ceiling. This suggests that the death occurred at around this time, which would be approximately 4:00-5:00 pm on November 29th, 2010.</t>
+    <t>Yes. The coroner noted that Dr. Nathan Gibson (Chief Psychiatrist) had initiated development of a Mental Health Act orientation and training program for all consultant psychiatrists to clarify the legal requirements for detaining and treating patients with personality disorders (page 20).</t>
+  </si>
+  <si>
+    <t>Immediate cause: Ligature compression of the neck (hanging) (page 14). Contributing factors: Substance abuse, personality disorder, pending court case, strained relationship with his mother, and recent absconding from psychiatric care (pages 9–13, 20)</t>
+  </si>
+  <si>
+    <t>Yes. The coroner concluded that Graylands Hospital staff provided reasonable and appropriate treatment and supervision. Although there were minor issues with record-keeping and a 45-minute delay in declaring him AWOL, these were not contributory to the death. Staff acted under the “least restrictive” principle of care (pages 15–17).</t>
+  </si>
+  <si>
+    <t>Yes. The case highlights the complex challenges in managing patients with personality and substance-use disorders and the need for clearer guidance under the Mental Health Act. It also emphasized system improvements in record-keeping, risk assessment, and staff training, which were implemented after the inquest (pages 18–20)</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, the deceased is a man who was born in Western Australia on October 23, 1982. He had a blended family, with his mother having been in three relationships before he was born. His step-father, whom he took as his surname, was from his mother's third relationship.
+The deceased suffered various personal and physical challenges throughout his life, including difficulties in school, drug abuse, and a serious accident involving a gunshot wound that resulted in him receiving the Disability Support Pension and substantial compensation payments.
+Unfortunately, without additional information or prior knowledge about the deceased, it is not possible to provide any further details or identify the specific person being referred to.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, the exact date of the death is not explicitly mentioned. However, it can be inferred that the death occurred around 4:10 pm on November 29th, 2010, when Mr. Ward discovered the deceased hanging from an electrical cord in the ceiling.</t>
   </si>
   <si>
     <t>The death occurred at 33A Snowbird Gardens, Joondalup.</t>
@@ -116,46 +135,73 @@
     <t>The cause of death was ligature compression of the neck (hanging).</t>
   </si>
   <si>
-    <t>The presiding coroner mentioned in the context is Ms R Hartley, who assisted by Ms M. Smith from the State Solicitors Office on behalf of the Health Department of WA.</t>
-  </si>
-  <si>
-    <t>The circumstances leading to the death were as follows:
-On the morning of Mr. Ward's return home from work at around 4:00pm, he noticed that the front door was locked and the deceased hanging by his neck with an electrical cord tied to a rafter through an open manhole in the ceiling. Mr. Ward cut the cord, applied chest compressions, and waited for ambulance paramedics to arrive. Unfortunately, upon arrival, the paramedics found the deceased showing no signs of life.
-The events unfolded as follows:
-- The day started with the couple leaving for work at 6:30am without noticing the deceased.
-- They returned home from work around 4:00pm and noticed the front door was locked, indicating that someone had been inside while they were away.
-- Upon entering the house, Mr. Ward found the deceased hanging by his neck.
-- He called 000 (the local emergency number) for assistance.
-- The paramedics arrived quickly but unfortunately found the deceased to be deceased.
-This tragic sequence of events ultimately led to the death of the individual.</t>
-  </si>
-  <si>
-    <t>Based on the provided context information, the deceased had a significant history of mental health issues and substance abuse-related problems. The following are some key points from their medical and mental health history:
-1. Admissions to mental health units multiple times (Joondalup Mental Health Unit in 2005 and Graylands twice: once voluntarily on June 28, 2006, after being admitted involuntarily on June 22, 2006) with diagnoses of psychotic symptoms of schizophrenia and drug withdrawal, amphetamine-induced psychosis, and psychosis secondary to use and IV amphetamine abuse.
-2. Episodes of suicidal self-harm, auditory hallucinations, paranoid psychotic episodes exacerbated by substance abuse.
-3. Use of amphetamines leading to amphetamine-induced psychosis.
-4. History of substance abuse with periods of non-use followed by resumption.
-5. Relationship issues including the end of a relationship and loss of accommodation, but these were noted as not contributing to suicidal ideation at the time of hospitalization in June 2006.
-This complex history highlights the interplay between mental health disorders and substance use, particularly amphetamines, which significantly impacted the deceased's life and required multiple admissions for treatment.</t>
-  </si>
-  <si>
-    <t>Based on the provided context information, it is not explicitly stated who testified or assisted in the inquest. However, it can be inferred that:
-* Coroner DH Mulligan was present and led the inquests.
-* Acting State Coroner Evelyn Vicker directed Coroner Mulligan to investigate the deaths after he became unable to make findings under s.25 of the Coroners Act 1996.
-* Interested parties who were present at the inquests before Coroner Mulligan were invited to make fresh or further submissions, indicating that some witnesses or experts may have participated in these proceedings.
-Unfortunately, the text does not provide specific information on individual witnesses or their roles in assisting with the inquest.</t>
-  </si>
-  <si>
-    <t>Yes, the deceased was considered a "person held in care" under the Coroners Act 1996. According to section 3 of the Coroners Act 1996 and section 22(1)a) of the Act, being an involuntary patient at Graylands Hospital at the time of death meets this criteria.</t>
-  </si>
-  <si>
-    <t>According to the context information, yes, there was evidence of substances in the body. The toxicology analysis found:
-* Therapeutic and sub-therapeutic levels of prescription medicines
+    <t>Based on the provided context information, the presiding coroner is Ms R Hartley.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, the circumstances leading to the death of the deceased are as follows:
+The deceased was found hanging from an electrical cord tied to a rafter through an open manhole in the ceiling by his wife upon returning home from work at approximately 4:00 pm. The front door was initially left unlocked by the deceased and his wife, but it was locked when they returned home, indicating that someone (likely the deceased) had entered the house before they did.
+Upon entering the house, Mr. Ward found the deceased hanging, and he immediately called emergency services. Paramedics arrived shortly after, but unfortunately, the deceased showed no signs of life.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, the deceased had a history of:
+1. Schizophrenia: The deceased was diagnosed with psychotic symptoms of schizophrenia in 2005 and again in 2006.
+2. Drug withdrawal: The deceased experienced drug withdrawal symptoms in 2005.
+3. Amphetamine use: The deceased used amphetamines on multiple occasions, including after a year of not using them, which led to amphetamine-induced psychosis in 2006.
+4. Suicidal behavior: The deceased attempted self-harm and expressed suicidal ideation on two separate occasions (in 2005 and 2007).
+5. Paranoid psychotic episodes: The deceased experienced ongoing paranoid psychotic episodes exacerbated by substance abuse, leading to hospitalizations and treatment.
+These medical and mental health conditions were significant enough to warrant multiple hospitalizations and interventions.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, it is unclear who specifically testified or assisted in the inquest. However, the following individuals are mentioned as having been involved:
+1. Coroner DH Mulligan
+2. Acting State Coroner Evelyn Vicker
+3. Interested parties (though no specific names are mentioned)
+It is also implied that other experts, such as healthcare professionals and witnesses, provided evidence during the inquests, but their identities are not specified.</t>
+  </si>
+  <si>
+    <t>Yes, according to section 3 of the Coroners Act 1996, the deceased was considered a 'person held in care'.</t>
+  </si>
+  <si>
+    <t>Yes, there was evidence of substances found in the deceased's body. The toxicology analysis showed:
+* Therapeutic levels of prescription medicines
+* Sub-therapeutic levels of prescription medicines
 * A low level of tetrahydrocannabinol (THC), indicating use of cannabis within 24 hours.
-No other specific details on other substances are mentioned.</t>
-  </si>
-  <si>
-    <t>The coroner did not address general issues separately from individual death findings but instead considered them relevant to the quality of supervision, treatment, and care of the deceased when connected to their deaths or potentially affecting those aspects. General evidence related to systemic issues at Graylands was provided to investigate its impact on specific deaths and allowed for a broader understanding of the context in which patients were treated. However, the coroner concluded that many general issues were not sufficiently connected to individual deaths to warrant comment under s.25.</t>
+Note: It does not mention alcohol, as it is stated "it is not clear whether he also abused alcohol".</t>
+  </si>
+  <si>
+    <t>The coroner's primary focus was on addressing the specific issues related to each death, rather than general systemic issues pertinent to Graylands. While evidence of systemic issues was presented, the coroner determined that not all issues were sufficiently connected to comment on them under section 25. The coroner did address some general issues relevant to the quality of supervision, treatment, and care at Graylands in their findings.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, it appears that the coroner did not make any explicit recommendations for future prevention. The text states that the coroner "did not address those general issues separately from a consideration of each death" and that many of the systemic issues mentioned in evidence were not sufficiently connected to all the respective deaths for the coroner to comment on them.
+However, it can be inferred that the coroner did make some recommendations based on the context information provided. The text mentions that the evidence related to general or systemic issues pertinent to Graylands was adduced "to investigate whether those issues had bearing on any or some of the deaths" and to allow the Court to comment on the quality of supervision, treatment, and care of the deceased patients.
+The fact that evidence regarding the condition of the buildings at Graylands was provided suggests that the coroner may have made recommendations related to environmental or physical conditions. The text states that "the physical environment of the wards would have been more therapeutic had the buildings been refurbished," which implies that the coroner considered the potential impact of these environmental factors on the treatment and care of patients.
+Overall, while the text does not explicitly state the coroner's recommendations for future prevention, it suggests that the coroner did consider systemic issues related to Graylands and may have made implicit recommendations for improvement in this regard.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, the immediate cause of death is ligature compression of the neck (hanging), as concluded by Chief Forensic Pathologist Dr. C T Cooke.
+The contributing factors that led to the hanging include:
+1. The unlocked front door, which allowed unauthorized access to the house.
+2. The electrical cord tied to a rafter through an open manhole in the ceiling, providing a means for the deceased to hang himself.
+3. The use of cannabis within 24 hours, as indicated by a low level of tetrahydrocannabinol, may have impaired judgment and increased the risk of suicidal behavior.
+It's worth noting that these contributing factors did not directly cause the death, but rather provided the circumstances in which the hanging occurred.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, it appears that the coroner did address some aspects of the quality of supervision, treatment, and care provided to the deceased. The relevant excerpts suggest that:
+1. The coroner considered general evidence related to systemic issues at Graylands, but determined that many of these issues were not sufficiently connected to each individual death to warrant comment under s.25.
+2. The coroner did evaluate the risk assessment and decision-making process surrounding the deceased's unescorted ground access, concluding that there was no reasonable basis for criticism.
+3. The coroner also considered the treating team's approach to treatment and acknowledged that there were legitimate criticisms if the treatment had been more restrictive.
+However, it is not explicitly stated whether the coroner evaluated the adequacy of supervision, treatment, or care provided in a comprehensive manner, taking into account each individual death. The excerpts suggest that the coroner's evaluation was context-dependent, focusing on specific aspects and connections to individual deaths rather than providing a broad assessment of the overall quality of care.
+In summary, while the coroner did evaluate certain aspects of supervision, treatment, and care, it is unclear whether this evaluation was comprehensive or solely focused on specific issues connected to individual deaths.</t>
+  </si>
+  <si>
+    <t>Yes, this case highlights several broader patterns and lessons relevant to public safety and institutional care. Here are a few:
+1. **Inadequate supervision and risk management**: The fact that the deceased was able to abscond from Graylands twice (on November 29th and December 7th) raises concerns about the effectiveness of the institution's supervision and risk management systems. This suggests that the institution may not have been adequately prepared to prevent or respond to such incidents.
+2. **Lack of adequate care planning**: The deceased's aggressive behavior, suicidal tendencies, and history of manipulating the system for his gratification suggest that he required more intensive and specialized care than was likely provided at Graylands. This highlights the importance of having adequate care plans in place for patients with complex needs.
+3. **Inadequate record-keeping and communication**: The lack of proper record-keeping of the deceased's ground access, as well as delays in declaring him AWOL after his second absconding, suggest that there were communication breakdowns between staff members and potentially between institutions.
+4. **Need for improved treatment approaches**: The fact that the deceased was able to manipulate the system to achieve his goals, despite being a "difficult patient," suggests that traditional treatment approaches may not be effective in managing complex mental health conditions.
+5. **Importance of adequate staffing ratios and training**: The incident highlights the need for adequate staffing ratios and training for staff members who work with patients with high-risk behaviors. This is particularly important in institutions where patients may pose a risk to themselves or others.
+6. **Need for better coordination between institutions**: The fact that the deceased was able to abscond twice, despite being on a suspended sentence of imprisonment, suggests that there may be gaps in communication and coordination between Graylands and other institutions involved in his care.
+These broader patterns and lessons highlight the need for improved institutional care, supervision, and risk management systems, as well as more effective treatment approaches and better communication and coordination between institutions.</t>
   </si>
 </sst>
 </file>
@@ -513,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -538,10 +584,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -552,10 +598,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -566,10 +612,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -580,10 +626,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -594,10 +640,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -608,10 +654,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -622,10 +668,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -636,10 +682,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -650,10 +696,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -664,10 +710,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -678,10 +724,66 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
